--- a/artfynd/A 15388-2026 artfynd.xlsx
+++ b/artfynd/A 15388-2026 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132528489</v>
+        <v>132528160</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582988</v>
+        <v>583014</v>
       </c>
       <c r="R2" t="n">
-        <v>7043530</v>
+        <v>7043497</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132528160</v>
+        <v>132524554</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583014</v>
+        <v>582944</v>
       </c>
       <c r="R3" t="n">
-        <v>7043497</v>
+        <v>7043846</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,19 +886,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132535188</v>
+        <v>132528489</v>
       </c>
       <c r="B4" t="n">
         <v>79333</v>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582780</v>
+        <v>582988</v>
       </c>
       <c r="R4" t="n">
-        <v>7043929</v>
+        <v>7043530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132524554</v>
+        <v>132535188</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,42 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582944</v>
+        <v>582780</v>
       </c>
       <c r="R5" t="n">
-        <v>7043846</v>
+        <v>7043929</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,22 +1100,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132528125</v>
+        <v>132526763</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,37 +1123,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583007</v>
+        <v>582909</v>
       </c>
       <c r="R6" t="n">
-        <v>7043504</v>
+        <v>7043694</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1197,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, högt upp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,22 +1217,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132526763</v>
+        <v>132528125</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,42 +1240,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582909</v>
+        <v>583007</v>
       </c>
       <c r="R7" t="n">
-        <v>7043694</v>
+        <v>7043504</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,12 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, högt upp</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,12 +1324,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132526843</v>
+        <v>132526588</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,34 +2120,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582929</v>
+        <v>582885</v>
       </c>
       <c r="R15" t="n">
-        <v>7043700</v>
+        <v>7043726</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,10 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132526588</v>
+        <v>132526843</v>
       </c>
       <c r="B16" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,34 +2227,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582885</v>
+        <v>582929</v>
       </c>
       <c r="R16" t="n">
-        <v>7043726</v>
+        <v>7043700</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2649,38 +2649,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132530025</v>
+        <v>132525138</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2689,13 +2688,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582918</v>
+        <v>582854</v>
       </c>
       <c r="R20" t="n">
-        <v>7043365</v>
+        <v>7043802</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,7 +2723,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2734,12 +2733,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,49 +2748,50 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132525138</v>
+        <v>132530025</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,13 +2800,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582854</v>
+        <v>582918</v>
       </c>
       <c r="R21" t="n">
-        <v>7043802</v>
+        <v>7043365</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2840,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2850,7 +2845,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,12 +2865,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132524526</v>
+        <v>132529790</v>
       </c>
       <c r="B23" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582951</v>
+        <v>582983</v>
       </c>
       <c r="R23" t="n">
-        <v>7043857</v>
+        <v>7043350</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3079,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,19 +3099,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132529790</v>
+        <v>132529143</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582983</v>
+        <v>582981</v>
       </c>
       <c r="R24" t="n">
-        <v>7043350</v>
+        <v>7043351</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,12 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,7 +3228,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132529143</v>
+        <v>132530085</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3254,7 +3259,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3263,13 +3268,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582981</v>
+        <v>582903</v>
       </c>
       <c r="R25" t="n">
-        <v>7043351</v>
+        <v>7043385</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,12 +3313,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,50 +3333,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132530085</v>
+        <v>132525807</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3380,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582903</v>
+        <v>582765</v>
       </c>
       <c r="R26" t="n">
-        <v>7043385</v>
+        <v>7043695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,7 +3419,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3425,12 +3429,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,49 +3456,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132525807</v>
+        <v>132524526</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582765</v>
+        <v>582951</v>
       </c>
       <c r="R27" t="n">
-        <v>7043695</v>
+        <v>7043857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4006,48 +4006,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132526796</v>
+        <v>132535010</v>
       </c>
       <c r="B32" t="n">
-        <v>83181</v>
+        <v>92614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>898</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582925</v>
+        <v>582768</v>
       </c>
       <c r="R32" t="n">
-        <v>7043696</v>
+        <v>7043891</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4101,60 +4101,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132535010</v>
+        <v>132526796</v>
       </c>
       <c r="B33" t="n">
-        <v>92614</v>
+        <v>83181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>898</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582768</v>
+        <v>582925</v>
       </c>
       <c r="R33" t="n">
-        <v>7043891</v>
+        <v>7043696</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,12 +4208,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132530216</v>
+        <v>132526109</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,16 +4342,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4371,13 +4371,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582892</v>
+        <v>582807</v>
       </c>
       <c r="R35" t="n">
-        <v>7043386</v>
+        <v>7043675</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4416,12 +4416,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4436,12 +4431,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4555,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132526109</v>
+        <v>132530216</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,16 +4561,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4595,13 +4590,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582807</v>
+        <v>582892</v>
       </c>
       <c r="R37" t="n">
-        <v>7043675</v>
+        <v>7043386</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4630,7 +4625,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4640,7 +4635,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4655,22 +4655,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132525951</v>
+        <v>132533969</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582796</v>
+        <v>582477</v>
       </c>
       <c r="R38" t="n">
-        <v>7043677</v>
+        <v>7043493</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4774,48 +4774,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132533969</v>
+        <v>132531463</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582477</v>
+        <v>582528</v>
       </c>
       <c r="R39" t="n">
-        <v>7043493</v>
+        <v>7043300</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4844,7 +4853,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4854,7 +4863,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,69 +4878,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132531463</v>
+        <v>132525951</v>
       </c>
       <c r="B40" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582528</v>
+        <v>582796</v>
       </c>
       <c r="R40" t="n">
-        <v>7043300</v>
+        <v>7043677</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4985,22 +4985,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132534952</v>
+        <v>132527201</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5008,34 +5008,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582767</v>
+        <v>582998</v>
       </c>
       <c r="R41" t="n">
-        <v>7043878</v>
+        <v>7043536</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5104,10 +5104,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132527201</v>
+        <v>132534155</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,34 +5115,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582998</v>
+        <v>582512</v>
       </c>
       <c r="R42" t="n">
-        <v>7043536</v>
+        <v>7043490</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5174,7 +5179,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5184,7 +5189,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5211,10 +5216,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132534155</v>
+        <v>132534952</v>
       </c>
       <c r="B43" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5222,39 +5227,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582512</v>
+        <v>582767</v>
       </c>
       <c r="R43" t="n">
-        <v>7043490</v>
+        <v>7043878</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 15388-2026 artfynd.xlsx
+++ b/artfynd/A 15388-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132528160</v>
+        <v>132524459</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583014</v>
+        <v>582955</v>
       </c>
       <c r="R2" t="n">
-        <v>7043497</v>
+        <v>7043865</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,62 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132524554</v>
+        <v>132535010</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>92689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582944</v>
+        <v>582768</v>
       </c>
       <c r="R3" t="n">
-        <v>7043846</v>
+        <v>7043891</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132528489</v>
+        <v>132525980</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582988</v>
+        <v>582808</v>
       </c>
       <c r="R4" t="n">
-        <v>7043530</v>
+        <v>7043666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132535188</v>
+        <v>132526406</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582780</v>
+        <v>582881</v>
       </c>
       <c r="R5" t="n">
-        <v>7043929</v>
+        <v>7043690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132526763</v>
+        <v>132526855</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,42 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582909</v>
+        <v>582943</v>
       </c>
       <c r="R6" t="n">
-        <v>7043694</v>
+        <v>7043688</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, högt upp</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132528125</v>
+        <v>132528893</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583007</v>
+        <v>582958</v>
       </c>
       <c r="R7" t="n">
-        <v>7043504</v>
+        <v>7043413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132526406</v>
+        <v>132533969</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582881</v>
+        <v>582477</v>
       </c>
       <c r="R8" t="n">
-        <v>7043690</v>
+        <v>7043493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132527759</v>
+        <v>132534952</v>
       </c>
       <c r="B9" t="n">
-        <v>58119</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,51 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582954</v>
+        <v>582767</v>
       </c>
       <c r="R9" t="n">
-        <v>7043507</v>
+        <v>7043878</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,22 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132528100</v>
+        <v>132526440</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>92406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,42 +1542,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582988</v>
+        <v>582854</v>
       </c>
       <c r="R10" t="n">
-        <v>7043500</v>
+        <v>7043666</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132524745</v>
+        <v>132526588</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,34 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582931</v>
+        <v>582885</v>
       </c>
       <c r="R11" t="n">
-        <v>7043806</v>
+        <v>7043726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132526926</v>
+        <v>132526796</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582942</v>
+        <v>582925</v>
       </c>
       <c r="R12" t="n">
-        <v>7043640</v>
+        <v>7043696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132526855</v>
+        <v>132524745</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1930,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582943</v>
+        <v>582931</v>
       </c>
       <c r="R13" t="n">
-        <v>7043688</v>
+        <v>7043806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132527265</v>
+        <v>132525094</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2033,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582993</v>
+        <v>582850</v>
       </c>
       <c r="R14" t="n">
-        <v>7043564</v>
+        <v>7043795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132526588</v>
+        <v>132525979</v>
       </c>
       <c r="B15" t="n">
-        <v>83181</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582885</v>
+        <v>582794</v>
       </c>
       <c r="R15" t="n">
-        <v>7043726</v>
+        <v>7043687</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2189,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,26 +2161,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132526843</v>
+        <v>132526091</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2247,14 +2204,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582929</v>
+        <v>582802</v>
       </c>
       <c r="R16" t="n">
-        <v>7043700</v>
+        <v>7043657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2296,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,53 +2280,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132531440</v>
+        <v>132526843</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582549</v>
+        <v>582929</v>
       </c>
       <c r="R17" t="n">
-        <v>7043308</v>
+        <v>7043700</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132526440</v>
+        <v>132526926</v>
       </c>
       <c r="B18" t="n">
-        <v>92378</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,37 +2398,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582854</v>
+        <v>582942</v>
       </c>
       <c r="R18" t="n">
-        <v>7043666</v>
+        <v>7043640</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,57 +2482,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132526623</v>
+        <v>132527201</v>
       </c>
       <c r="B19" t="n">
-        <v>83315</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582888</v>
+        <v>582998</v>
       </c>
       <c r="R19" t="n">
-        <v>7043738</v>
+        <v>7043536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132525138</v>
+        <v>132527265</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,38 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582854</v>
+        <v>582993</v>
       </c>
       <c r="R20" t="n">
-        <v>7043802</v>
+        <v>7043564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2733,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,53 +2708,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132530025</v>
+        <v>132528125</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582918</v>
+        <v>583007</v>
       </c>
       <c r="R21" t="n">
-        <v>7043365</v>
+        <v>7043504</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2835,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,12 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,65 +2803,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132527461</v>
+        <v>132528489</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582955</v>
+        <v>582988</v>
       </c>
       <c r="R22" t="n">
-        <v>7043527</v>
+        <v>7043530</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2952,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2962,12 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,65 +2910,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132529790</v>
+        <v>132528797</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582983</v>
+        <v>582949</v>
       </c>
       <c r="R23" t="n">
-        <v>7043350</v>
+        <v>7043442</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3069,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,12 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,65 +3017,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132529143</v>
+        <v>132529071</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582981</v>
+        <v>582967</v>
       </c>
       <c r="R24" t="n">
-        <v>7043351</v>
+        <v>7043393</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3186,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,62 +3124,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132530085</v>
+        <v>132535188</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582903</v>
+        <v>582780</v>
       </c>
       <c r="R25" t="n">
-        <v>7043385</v>
+        <v>7043929</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,12 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132525807</v>
+        <v>132918230</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,38 +3254,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582765</v>
+        <v>582819</v>
       </c>
       <c r="R26" t="n">
-        <v>7043695</v>
+        <v>7043514</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,22 +3308,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3456,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132524526</v>
+        <v>132526623</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>83358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,39 +3361,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582951</v>
+        <v>582888</v>
       </c>
       <c r="R27" t="n">
-        <v>7043857</v>
+        <v>7043738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3531,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3541,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132529071</v>
+        <v>132525951</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3603,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582967</v>
+        <v>582796</v>
       </c>
       <c r="R28" t="n">
-        <v>7043393</v>
+        <v>7043677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3648,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132525094</v>
+        <v>132529475</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3686,34 +3575,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Sundmotjärnen, Sundmotjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582850</v>
+        <v>583033</v>
       </c>
       <c r="R29" t="n">
-        <v>7043795</v>
+        <v>7043352</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3755,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3782,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132529475</v>
+        <v>132918313</v>
       </c>
       <c r="B30" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,17 +3702,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundmotjärnen, Sundmotjärnen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583033</v>
+        <v>582793</v>
       </c>
       <c r="R30" t="n">
-        <v>7043352</v>
+        <v>7043564</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3847,22 +3736,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3877,39 +3766,39 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132527204</v>
+        <v>132524526</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3925,17 +3814,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582947</v>
+        <v>582951</v>
       </c>
       <c r="R31" t="n">
-        <v>7043553</v>
+        <v>7043857</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3974,12 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,57 +3878,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132535010</v>
+        <v>132524554</v>
       </c>
       <c r="B32" t="n">
-        <v>92614</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundmoberget, Sundmoberget, Ång</t>
+          <t>Långforsen, Långforsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582768</v>
+        <v>582944</v>
       </c>
       <c r="R32" t="n">
-        <v>7043891</v>
+        <v>7043846</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4076,7 +3965,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4086,7 +3975,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,48 +4002,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132526796</v>
+        <v>132526109</v>
       </c>
       <c r="B33" t="n">
-        <v>83181</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582925</v>
+        <v>582807</v>
       </c>
       <c r="R33" t="n">
-        <v>7043696</v>
+        <v>7043675</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4183,7 +4077,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4193,7 +4087,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,49 +4102,50 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132529329</v>
+        <v>132531440</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4259,13 +4154,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582998</v>
+        <v>582549</v>
       </c>
       <c r="R34" t="n">
-        <v>7043351</v>
+        <v>7043308</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4294,7 +4189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4199,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,14 +4226,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132526109</v>
+        <v>132534155</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4371,13 +4266,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582807</v>
+        <v>582512</v>
       </c>
       <c r="R35" t="n">
-        <v>7043675</v>
+        <v>7043490</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4406,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4416,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4431,22 +4326,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132525979</v>
+        <v>132525197</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,34 +4349,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582794</v>
+        <v>582828</v>
       </c>
       <c r="R36" t="n">
-        <v>7043687</v>
+        <v>7043790</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4513,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4523,7 +4423,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4550,10 +4455,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132530216</v>
+        <v>132525548</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,7 +4486,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4590,13 +4495,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582892</v>
+        <v>582773</v>
       </c>
       <c r="R37" t="n">
-        <v>7043386</v>
+        <v>7043726</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4625,7 +4530,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4635,7 +4540,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4655,22 +4560,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132533969</v>
+        <v>132526763</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,37 +4583,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582477</v>
+        <v>582909</v>
       </c>
       <c r="R38" t="n">
-        <v>7043493</v>
+        <v>7043694</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4737,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4657,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, högt upp</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4762,54 +4677,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132531463</v>
+        <v>132527204</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4818,10 +4729,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582528</v>
+        <v>582947</v>
       </c>
       <c r="R39" t="n">
-        <v>7043300</v>
+        <v>7043553</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4853,7 +4764,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4863,7 +4774,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,10 +4806,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132525951</v>
+        <v>132527461</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4901,37 +4817,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582796</v>
+        <v>582955</v>
       </c>
       <c r="R40" t="n">
-        <v>7043677</v>
+        <v>7043527</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4960,7 +4881,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4970,7 +4891,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4985,22 +4911,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132527201</v>
+        <v>132528100</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5008,34 +4934,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långforsen, Långforsen, Ång</t>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582998</v>
+        <v>582988</v>
       </c>
       <c r="R41" t="n">
-        <v>7043536</v>
+        <v>7043500</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,7 +4998,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5077,7 +5008,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5104,10 +5040,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132534155</v>
+        <v>132528671</v>
       </c>
       <c r="B42" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,16 +5051,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5144,13 +5080,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582512</v>
+        <v>582977</v>
       </c>
       <c r="R42" t="n">
-        <v>7043490</v>
+        <v>7043467</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5189,7 +5125,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5204,22 +5145,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132534952</v>
+        <v>132529143</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5227,37 +5168,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582767</v>
+        <v>582981</v>
       </c>
       <c r="R43" t="n">
-        <v>7043878</v>
+        <v>7043351</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5286,7 +5232,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5296,7 +5242,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,49 +5262,50 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132529033</v>
+        <v>132529790</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5362,13 +5314,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582962</v>
+        <v>582983</v>
       </c>
       <c r="R44" t="n">
-        <v>7043380</v>
+        <v>7043350</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5349,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5359,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,22 +5379,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132930824</v>
+        <v>132530025</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5474,10 +5431,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582883</v>
+        <v>582918</v>
       </c>
       <c r="R45" t="n">
-        <v>7043524</v>
+        <v>7043365</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5504,27 +5461,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5551,10 +5508,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132918230</v>
+        <v>132530085</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5562,34 +5519,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582819</v>
+        <v>582903</v>
       </c>
       <c r="R46" t="n">
-        <v>7043514</v>
+        <v>7043385</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5616,22 +5578,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5658,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132918313</v>
+        <v>132530216</v>
       </c>
       <c r="B47" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5669,37 +5636,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582793</v>
+        <v>582892</v>
       </c>
       <c r="R47" t="n">
-        <v>7043564</v>
+        <v>7043386</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5723,22 +5695,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5753,15 +5730,924 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132930824</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>582883</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7043524</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132527759</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>582954</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7043507</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132525138</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>582854</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7043802</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132525807</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>582765</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7043695</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132528160</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långforsen, Långforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>583014</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7043497</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132529033</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>582962</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7043380</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132529329</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>582998</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7043351</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132531463</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>582528</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7043300</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15388-2026 artfynd.xlsx
+++ b/artfynd/A 15388-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132524459</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132535010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533969</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526440</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526588</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526796</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132524745</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525094</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525979</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526091</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526843</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526926</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527201</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527265</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528125</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528489</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528797</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529071</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132535188</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918230</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526623</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525951</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529475</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918313</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3887,6 +4037,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132524526</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3999,6 +4154,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132524554</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4111,6 +4271,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526109</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4223,6 +4388,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132531440</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4335,6 +4505,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534155</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4452,6 +4627,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525197</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4569,6 +4749,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525548</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4686,6 +4871,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526763</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4803,6 +4993,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527204</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4920,6 +5115,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527461</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5037,6 +5237,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528100</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5154,6 +5359,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528671</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5271,6 +5481,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529143</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5388,6 +5603,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529790</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5505,6 +5725,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132530025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5622,6 +5847,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132530085</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5739,6 +5969,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132530216</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5856,6 +6091,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132930824</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5977,6 +6217,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527759</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6088,6 +6333,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525138</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6199,6 +6449,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525807</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6310,6 +6565,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528160</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6421,6 +6681,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529033</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6532,6 +6797,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132529329</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6648,8 +6918,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132531463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>